--- a/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Class_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Class_by_Sample_Type.xlsx
@@ -825,10 +825,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>21.9787154411997</v>
+        <v>21.9799582045037</v>
       </c>
       <c r="D2" t="n">
-        <v>0.490836988744614</v>
+        <v>0.490888986996894</v>
       </c>
     </row>
     <row r="3">
@@ -839,10 +839,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>8.76692677984079</v>
+        <v>8.76657567358605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.199941940599583</v>
+        <v>0.201058681955327</v>
       </c>
     </row>
     <row r="4">
@@ -853,10 +853,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8.37598650030049</v>
+        <v>8.37538719628584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.184735816032211</v>
+        <v>0.184717350896407</v>
       </c>
     </row>
     <row r="5">
@@ -867,10 +867,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>4.7955500050665</v>
+        <v>4.79608639224169</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0954406827325604</v>
+        <v>0.0954508015339451</v>
       </c>
     </row>
     <row r="6">
@@ -881,10 +881,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58632514697018</v>
+        <v>4.58631644613354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.265096385530426</v>
+        <v>0.265091787475345</v>
       </c>
     </row>
     <row r="7">
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.96489566136487</v>
+        <v>3.96522201435841</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0964690180953352</v>
+        <v>0.0964813776637118</v>
       </c>
     </row>
     <row r="8">
@@ -909,10 +909,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7243080649101</v>
+        <v>3.72399152550915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.053899320325139</v>
+        <v>0.0538939796108262</v>
       </c>
     </row>
     <row r="9">
@@ -923,10 +923,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.66690114156154</v>
+        <v>3.66666827455714</v>
       </c>
       <c r="D9" t="n">
-        <v>0.140760881755757</v>
+        <v>0.140747505819984</v>
       </c>
     </row>
     <row r="10">
@@ -937,10 +937,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.57051007852822</v>
+        <v>3.57038310021036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0674328441142328</v>
+        <v>0.0674305129007403</v>
       </c>
     </row>
     <row r="11">
@@ -951,10 +951,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.21105032549323</v>
+        <v>3.21110959330595</v>
       </c>
       <c r="D11" t="n">
-        <v>0.429298584230496</v>
+        <v>0.429309077052021</v>
       </c>
     </row>
     <row r="12">
@@ -965,10 +965,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>3.18513984798712</v>
+        <v>3.18497137478922</v>
       </c>
       <c r="D12" t="n">
-        <v>0.114016331705178</v>
+        <v>0.114008461300709</v>
       </c>
     </row>
     <row r="13">
@@ -979,10 +979,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>3.04891292336428</v>
+        <v>3.04910811408604</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0562950685147359</v>
+        <v>0.0562993834594735</v>
       </c>
     </row>
     <row r="14">
@@ -993,10 +993,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>2.90693837065784</v>
+        <v>2.9078237697701</v>
       </c>
       <c r="D14" t="n">
-        <v>0.848514761712234</v>
+        <v>0.848774383302174</v>
       </c>
     </row>
     <row r="15">
@@ -1007,10 +1007,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.83886542492783</v>
+        <v>1.83873120338501</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0330914423985603</v>
+        <v>0.033088796804791</v>
       </c>
     </row>
     <row r="16">
@@ -1021,10 +1021,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.75106759017128</v>
+        <v>1.75138898300309</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1667718000852</v>
+        <v>0.166801682503198</v>
       </c>
     </row>
     <row r="17">
@@ -1035,10 +1035,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.55734061781472</v>
+        <v>1.55728726615353</v>
       </c>
       <c r="D17" t="n">
-        <v>0.522080141675004</v>
+        <v>0.522067960073351</v>
       </c>
     </row>
     <row r="18">
@@ -1049,10 +1049,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.48377840736855</v>
+        <v>1.48385256396774</v>
       </c>
       <c r="D18" t="n">
-        <v>0.122826069081501</v>
+        <v>0.122840981953677</v>
       </c>
     </row>
     <row r="19">
@@ -1063,10 +1063,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.23047170899452</v>
+        <v>1.230360372418</v>
       </c>
       <c r="D19" t="n">
-        <v>0.151613823845976</v>
+        <v>0.151602610044505</v>
       </c>
     </row>
     <row r="20">
@@ -1077,10 +1077,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1616757331315</v>
+        <v>1.16178318287229</v>
       </c>
       <c r="D20" t="n">
-        <v>0.176434462685899</v>
+        <v>0.176455029969349</v>
       </c>
     </row>
     <row r="21">
@@ -1091,10 +1091,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.09703163996876</v>
+        <v>1.0953890090959</v>
       </c>
       <c r="D21" t="n">
-        <v>0.126910254393261</v>
+        <v>0.134578545684737</v>
       </c>
     </row>
     <row r="22">
@@ -1105,10 +1105,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.968131272611667</v>
+        <v>0.96806432673786</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0185739043304981</v>
+        <v>0.0185721689859961</v>
       </c>
     </row>
     <row r="23">
@@ -1119,10 +1119,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.857836275493774</v>
+        <v>0.857814410525154</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0857934487131631</v>
+        <v>0.0857903118571765</v>
       </c>
     </row>
     <row r="24">
@@ -1133,10 +1133,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.848467110325538</v>
+        <v>0.84830527092907</v>
       </c>
       <c r="D24" t="n">
-        <v>0.289379225813157</v>
+        <v>0.289314746281158</v>
       </c>
     </row>
     <row r="25">
@@ -1147,10 +1147,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.818459234610933</v>
+        <v>0.818617242566109</v>
       </c>
       <c r="D25" t="n">
-        <v>0.067497634553842</v>
+        <v>0.067509913679081</v>
       </c>
     </row>
     <row r="26">
@@ -1161,10 +1161,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.808472130103592</v>
+        <v>0.80850725443698</v>
       </c>
       <c r="D26" t="n">
-        <v>0.154569455135979</v>
+        <v>0.154585340843082</v>
       </c>
     </row>
     <row r="27">
@@ -1175,10 +1175,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.745095754293287</v>
+        <v>0.745126362573919</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0231663501894589</v>
+        <v>0.0231683694809714</v>
       </c>
     </row>
     <row r="28">
@@ -1189,10 +1189,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.717789083657777</v>
+        <v>0.717720333482241</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0904521077802339</v>
+        <v>0.0904446384621796</v>
       </c>
     </row>
     <row r="29">
@@ -1203,10 +1203,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.546939917718448</v>
+        <v>0.5469106672692</v>
       </c>
       <c r="D29" t="n">
-        <v>0.236708808884444</v>
+        <v>0.23669411707758</v>
       </c>
     </row>
     <row r="30">
@@ -1217,10 +1217,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.528952935250389</v>
+        <v>0.529021771158293</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0193981835922004</v>
+        <v>0.0194002915741415</v>
       </c>
     </row>
     <row r="31">
@@ -1231,10 +1231,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.430293030354796</v>
+        <v>0.430362935082194</v>
       </c>
       <c r="D31" t="n">
-        <v>0.106578730709796</v>
+        <v>0.106595560404305</v>
       </c>
     </row>
     <row r="32">
@@ -1245,10 +1245,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.419048522431741</v>
+        <v>0.419020322211645</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0232657073408555</v>
+        <v>0.0232625777419894</v>
       </c>
     </row>
     <row r="33">
@@ -1259,10 +1259,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.385966495665358</v>
+        <v>0.386046041583528</v>
       </c>
       <c r="D33" t="n">
-        <v>0.022520171705642</v>
+        <v>0.0225260377604896</v>
       </c>
     </row>
     <row r="34">
@@ -1273,10 +1273,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.346401561761411</v>
+        <v>0.346406996330817</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00848242083577107</v>
+        <v>0.00848308271124754</v>
       </c>
     </row>
     <row r="35">
@@ -1287,10 +1287,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.336323276074375</v>
+        <v>0.336320017196861</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0303813994566529</v>
+        <v>0.0303835110090498</v>
       </c>
     </row>
     <row r="36">
@@ -1301,10 +1301,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.316077690942096</v>
+        <v>0.316104971437568</v>
       </c>
       <c r="D36" t="n">
-        <v>0.010231484938941</v>
+        <v>0.0102324518680789</v>
       </c>
     </row>
     <row r="37">
@@ -1315,10 +1315,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.310150166875274</v>
+        <v>0.310114714012385</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0685769544517772</v>
+        <v>0.0685672363066828</v>
       </c>
     </row>
     <row r="38">
@@ -1329,10 +1329,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.295566559308626</v>
+        <v>0.295571086745162</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00808169739661992</v>
+        <v>0.00808183984791037</v>
       </c>
     </row>
     <row r="39">
@@ -1343,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.242674225434993</v>
+        <v>0.242650323142323</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0224444037160852</v>
+        <v>0.0224418613647339</v>
       </c>
     </row>
     <row r="40">
@@ -1357,10 +1357,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.235791615880213</v>
+        <v>0.235759726724195</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0947939764946072</v>
+        <v>0.0947801490926459</v>
       </c>
     </row>
     <row r="41">
@@ -1371,10 +1371,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.226671778921371</v>
+        <v>0.226639648319221</v>
       </c>
       <c r="D41" t="n">
-        <v>0.030802944107052</v>
+        <v>0.0307982994618997</v>
       </c>
     </row>
     <row r="42">
@@ -1385,10 +1385,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.217412479600799</v>
+        <v>0.217459208654182</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0357391999950631</v>
+        <v>0.0357468425513277</v>
       </c>
     </row>
     <row r="43">
@@ -1399,10 +1399,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.215133548017827</v>
+        <v>0.215139633004419</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00765016869487261</v>
+        <v>0.00765023903483435</v>
       </c>
     </row>
     <row r="44">
@@ -1413,10 +1413,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.214486460596688</v>
+        <v>0.214470579235682</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0387518958895776</v>
+        <v>0.0387484901861466</v>
       </c>
     </row>
     <row r="45">
@@ -1427,10 +1427,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.213394528600517</v>
+        <v>0.213419785319753</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0615196028841004</v>
+        <v>0.0615402836652481</v>
       </c>
     </row>
     <row r="46">
@@ -1441,10 +1441,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.188935625579661</v>
+        <v>0.188942846136338</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0106093756356102</v>
+        <v>0.0106093439118613</v>
       </c>
     </row>
     <row r="47">
@@ -1455,10 +1455,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.184825372319607</v>
+        <v>0.18480018114175</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0604408082587919</v>
+        <v>0.0604306433345011</v>
       </c>
     </row>
     <row r="48">
@@ -1469,10 +1469,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.182669834283909</v>
+        <v>0.182662735135597</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0274990566320673</v>
+        <v>0.0275001011227362</v>
       </c>
     </row>
     <row r="49">
@@ -1483,10 +1483,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.149037282460456</v>
+        <v>0.149033893417521</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00490041538477011</v>
+        <v>0.00490041359945902</v>
       </c>
     </row>
     <row r="50">
@@ -1497,10 +1497,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.13028445282164</v>
+        <v>0.130277976533951</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0132887801066265</v>
+        <v>0.0132870685725215</v>
       </c>
     </row>
     <row r="51">
@@ -1511,10 +1511,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.118686057287232</v>
+        <v>0.118722903980699</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0288540778614486</v>
+        <v>0.0288633279015669</v>
       </c>
     </row>
     <row r="52">
@@ -1525,10 +1525,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.114909437458452</v>
+        <v>0.114891980988895</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0178909320574738</v>
+        <v>0.0178852675083426</v>
       </c>
     </row>
     <row r="53">
@@ -1539,10 +1539,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.109250748394383</v>
+        <v>0.109268448100416</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0156842513821768</v>
+        <v>0.0156864711753446</v>
       </c>
     </row>
     <row r="54">
@@ -1553,7 +1553,7 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0989603543565518</v>
+        <v>0.0989321799505745</v>
       </c>
       <c r="D54"/>
     </row>
@@ -1565,10 +1565,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0931332790647367</v>
+        <v>0.0931309996902721</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0327415527241503</v>
+        <v>0.0327398335275147</v>
       </c>
     </row>
     <row r="56">
@@ -1579,10 +1579,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0904120440215771</v>
+        <v>0.0904003250131124</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00899418206847615</v>
+        <v>0.00899305994560171</v>
       </c>
     </row>
     <row r="57">
@@ -1593,7 +1593,7 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0828081315444811</v>
+        <v>0.082792415700007</v>
       </c>
       <c r="D57"/>
     </row>
@@ -1605,10 +1605,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0774329262628541</v>
+        <v>0.0774453642762558</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00543996167827075</v>
+        <v>0.00544061141138761</v>
       </c>
     </row>
     <row r="59">
@@ -1619,10 +1619,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.07513007830488</v>
+        <v>0.0751270586034985</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00978986799512828</v>
+        <v>0.00978935660872495</v>
       </c>
     </row>
     <row r="60">
@@ -1633,10 +1633,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0597653768784115</v>
+        <v>0.059774455983255</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00368020830547326</v>
+        <v>0.00368083984263925</v>
       </c>
     </row>
     <row r="61">
@@ -1647,10 +1647,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0555176044620979</v>
+        <v>0.0555219006253551</v>
       </c>
       <c r="D61" t="n">
-        <v>0.010882824261015</v>
+        <v>0.0108834020325943</v>
       </c>
     </row>
     <row r="62">
@@ -1661,10 +1661,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0554446595183428</v>
+        <v>0.0554444320279701</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00370121646356186</v>
+        <v>0.00370068759532628</v>
       </c>
     </row>
     <row r="63">
@@ -1675,10 +1675,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0530687171392698</v>
+        <v>0.0530674085948034</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00649743587405406</v>
+        <v>0.00649680300087323</v>
       </c>
     </row>
     <row r="64">
@@ -1689,10 +1689,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0510835085367868</v>
+        <v>0.0510840033290636</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00409622825963514</v>
+        <v>0.00409602160930587</v>
       </c>
     </row>
     <row r="65">
@@ -1703,10 +1703,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0472670529958941</v>
+        <v>0.0472737734920091</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00300145703035621</v>
+        <v>0.00300199852633558</v>
       </c>
     </row>
     <row r="66">
@@ -1717,10 +1717,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0439272059655816</v>
+        <v>0.0439311193068667</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00281672021647584</v>
+        <v>0.00281725961473784</v>
       </c>
     </row>
     <row r="67">
@@ -1731,7 +1731,7 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0425454373998597</v>
+        <v>0.0425428850299084</v>
       </c>
       <c r="D67"/>
     </row>
@@ -1743,10 +1743,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0422022374185856</v>
+        <v>0.042212466894678</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00704739422470973</v>
+        <v>0.00704998638812337</v>
       </c>
     </row>
     <row r="69">
@@ -1757,10 +1757,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0401099282992982</v>
+        <v>0.0401154360391381</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00899770989979867</v>
+        <v>0.00899976873991183</v>
       </c>
     </row>
     <row r="70">
@@ -1771,10 +1771,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0399729323137417</v>
+        <v>0.039965354638804</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0223933769823801</v>
+        <v>0.0223895389603966</v>
       </c>
     </row>
     <row r="71">
@@ -1785,10 +1785,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0397407192602098</v>
+        <v>0.0397402698905676</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00804735726344126</v>
+        <v>0.00804510732230997</v>
       </c>
     </row>
     <row r="72">
@@ -1799,7 +1799,7 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0390031233074237</v>
+        <v>0.0389926269564989</v>
       </c>
       <c r="D72"/>
     </row>
@@ -1811,10 +1811,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0345293411473442</v>
+        <v>0.0345266407570089</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00520283223202059</v>
+        <v>0.00520217535474315</v>
       </c>
     </row>
     <row r="74">
@@ -1825,10 +1825,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0345161871410933</v>
+        <v>0.0345189461904412</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00893760982438653</v>
+        <v>0.00893874389584192</v>
       </c>
     </row>
     <row r="75">
@@ -1839,10 +1839,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.029074987612196</v>
+        <v>0.0290714171741318</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00673156812733868</v>
+        <v>0.00672960975019451</v>
       </c>
     </row>
     <row r="76">
@@ -1853,10 +1853,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0265305095280331</v>
+        <v>0.0265273544123701</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00902388670407662</v>
+        <v>0.00902092654466737</v>
       </c>
     </row>
     <row r="77">
@@ -1867,10 +1867,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0256911195041461</v>
+        <v>0.0256851355435961</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0171909980378978</v>
+        <v>0.0171872123055681</v>
       </c>
     </row>
     <row r="78">
@@ -1881,10 +1881,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0250270664044901</v>
+        <v>0.0250266151135585</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00331625301899882</v>
+        <v>0.00331646493945638</v>
       </c>
     </row>
     <row r="79">
@@ -1895,10 +1895,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.02468760335681</v>
+        <v>0.0246914905929518</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0039508930761767</v>
+        <v>0.00395200937404464</v>
       </c>
     </row>
     <row r="80">
@@ -1909,10 +1909,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0240757178501265</v>
+        <v>0.0240772699490756</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00316824594110922</v>
+        <v>0.00316770989894922</v>
       </c>
     </row>
     <row r="81">
@@ -1923,10 +1923,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0237037434801785</v>
+        <v>0.0237031496639221</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00682263226104706</v>
+        <v>0.00682189265494413</v>
       </c>
     </row>
     <row r="82">
@@ -1937,10 +1937,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0222829613277351</v>
+        <v>0.0222802524851444</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00249317401432221</v>
+        <v>0.0024928912067423</v>
       </c>
     </row>
     <row r="83">
@@ -1951,10 +1951,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0220213012374824</v>
+        <v>0.0220279005835373</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0143380396374616</v>
+        <v>0.0143421073785844</v>
       </c>
     </row>
     <row r="84">
@@ -1965,10 +1965,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0219029899198959</v>
+        <v>0.0219035922459783</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00308503511636453</v>
+        <v>0.00308526430285486</v>
       </c>
     </row>
     <row r="85">
@@ -1979,10 +1979,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0200565710310945</v>
+        <v>0.020054281611199</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00367870256286118</v>
+        <v>0.00367732895311549</v>
       </c>
     </row>
     <row r="86">
@@ -1993,10 +1993,10 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0189050723134356</v>
+        <v>0.0189074176699697</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00270797388873265</v>
+        <v>0.00270831467486109</v>
       </c>
     </row>
     <row r="87">
@@ -2007,10 +2007,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.015449903512412</v>
+        <v>0.0154465809187106</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00589527197923556</v>
+        <v>0.0058945862179202</v>
       </c>
     </row>
     <row r="88">
@@ -2021,10 +2021,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0133806886427356</v>
+        <v>0.0133831671015731</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0011638019432493</v>
+        <v>0.0011639953494407</v>
       </c>
     </row>
     <row r="89">
@@ -2035,10 +2035,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.012735768643081</v>
+        <v>0.0127365993963008</v>
       </c>
       <c r="D89" t="n">
-        <v>0.000804625879620015</v>
+        <v>0.00080439076786438</v>
       </c>
     </row>
     <row r="90">
@@ -2049,7 +2049,7 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0115894268937818</v>
+        <v>0.0115854025923441</v>
       </c>
       <c r="D90"/>
     </row>
@@ -2061,10 +2061,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0105078088343309</v>
+        <v>0.0105113755676532</v>
       </c>
       <c r="D91" t="n">
-        <v>0.000695693990503509</v>
+        <v>0.000696749609857311</v>
       </c>
     </row>
     <row r="92">
@@ -2075,7 +2075,7 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0104810523897978</v>
+        <v>0.0104799249606146</v>
       </c>
       <c r="D92"/>
     </row>
@@ -2087,10 +2087,10 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0104059400245581</v>
+        <v>0.0104062662942485</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00178480716024466</v>
+        <v>0.00178472513990436</v>
       </c>
     </row>
     <row r="94">
@@ -2101,10 +2101,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0102809022265025</v>
+        <v>0.0102788203664386</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00662758978737952</v>
+        <v>0.00662641101662855</v>
       </c>
     </row>
     <row r="95">
@@ -2115,7 +2115,7 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00880533662757085</v>
+        <v>0.00880743994783173</v>
       </c>
       <c r="D95"/>
     </row>
@@ -2127,10 +2127,10 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.00829950529628536</v>
+        <v>0.00829750682753266</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00488196017629464</v>
+        <v>0.00488004694521971</v>
       </c>
     </row>
     <row r="97">
@@ -2141,10 +2141,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.00751019018255811</v>
+        <v>0.00751056931079806</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00155233406502311</v>
+        <v>0.00155267126757225</v>
       </c>
     </row>
     <row r="98">
@@ -2155,7 +2155,7 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00730959158723154</v>
+        <v>0.00730789592149665</v>
       </c>
       <c r="D98"/>
     </row>
@@ -2167,10 +2167,10 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0072583208583217</v>
+        <v>0.00725821740919093</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00165758289577762</v>
+        <v>0.00165753410433041</v>
       </c>
     </row>
     <row r="100">
@@ -2181,7 +2181,7 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00650465609108132</v>
+        <v>0.00650168463607803</v>
       </c>
       <c r="D100"/>
     </row>
@@ -2193,10 +2193,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.00460920863352648</v>
+        <v>0.00460949360120326</v>
       </c>
       <c r="D101" t="n">
-        <v>0.000478895956824243</v>
+        <v>0.000479108282563972</v>
       </c>
     </row>
     <row r="102">
@@ -2207,7 +2207,7 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00418940151357515</v>
+        <v>0.00418838416681624</v>
       </c>
       <c r="D102"/>
     </row>
@@ -2219,7 +2219,7 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00370255380494725</v>
+        <v>0.00370190826886904</v>
       </c>
       <c r="D103"/>
     </row>
@@ -2231,10 +2231,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00358528882876715</v>
+        <v>0.00358551861146706</v>
       </c>
       <c r="D104" t="n">
-        <v>0.000338815391567233</v>
+        <v>0.000338416431745612</v>
       </c>
     </row>
     <row r="105">
@@ -2245,10 +2245,10 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00339769476234774</v>
+        <v>0.00339711378735422</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00028522185253323</v>
+        <v>0.000284404844539178</v>
       </c>
     </row>
     <row r="106">
@@ -2259,7 +2259,7 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00311996585764075</v>
+        <v>0.00311854059579324</v>
       </c>
       <c r="D106"/>
     </row>
@@ -2271,7 +2271,7 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00305726011193323</v>
+        <v>0.00305638642701374</v>
       </c>
       <c r="D107"/>
     </row>
@@ -2283,7 +2283,7 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00253401467009964</v>
+        <v>0.00253285708229416</v>
       </c>
       <c r="D108"/>
     </row>
@@ -2295,7 +2295,7 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00201293664975059</v>
+        <v>0.00201328707765308</v>
       </c>
       <c r="D109"/>
     </row>
@@ -2307,10 +2307,10 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00199761522201514</v>
+        <v>0.00199834617169647</v>
       </c>
       <c r="D110" t="n">
-        <v>0.000186058412341193</v>
+        <v>0.000185877455545797</v>
       </c>
     </row>
     <row r="111">
@@ -2321,7 +2321,7 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.001954640485684</v>
+        <v>0.00195471872630317</v>
       </c>
       <c r="D111"/>
     </row>
@@ -2333,10 +2333,10 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00178333944973448</v>
+        <v>0.00178379476215956</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000801020496358377</v>
+        <v>0.000801552583773679</v>
       </c>
     </row>
     <row r="113">
@@ -2347,7 +2347,7 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00177541715051518</v>
+        <v>0.00177542785482386</v>
       </c>
       <c r="D113"/>
     </row>
@@ -2359,10 +2359,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00172227795480832</v>
+        <v>0.00172358291115443</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00017926116801792</v>
+        <v>0.00017928492614524</v>
       </c>
     </row>
     <row r="115">
@@ -2373,7 +2373,7 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00165785321964755</v>
+        <v>0.00165941172007079</v>
       </c>
       <c r="D115"/>
     </row>
@@ -2385,10 +2385,10 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00151293493487176</v>
+        <v>0.00151224379639819</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00017263970465586</v>
+        <v>0.000172560839438855</v>
       </c>
     </row>
     <row r="117">
@@ -2399,7 +2399,7 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00139537100400414</v>
+        <v>0.00139600354805577</v>
       </c>
       <c r="D117"/>
     </row>
@@ -2411,7 +2411,7 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00124148407860272</v>
+        <v>0.00124091694422617</v>
       </c>
       <c r="D118"/>
     </row>
@@ -2423,10 +2423,10 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00123647658758674</v>
+        <v>0.0012363599679094</v>
       </c>
       <c r="D119" t="n">
-        <v>0.000275550627961508</v>
+        <v>0.000275107806530468</v>
       </c>
     </row>
     <row r="120">
@@ -2437,10 +2437,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00122093094383565</v>
+        <v>0.00122156847101236</v>
       </c>
       <c r="D120" t="n">
-        <v>0.000123347749455727</v>
+        <v>0.000123397049933789</v>
       </c>
     </row>
     <row r="121">
@@ -2451,7 +2451,7 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00112982450281364</v>
+        <v>0.0011293083767303</v>
       </c>
       <c r="D121"/>
     </row>
@@ -2463,7 +2463,7 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00110359122898367</v>
+        <v>0.00110308708677645</v>
       </c>
       <c r="D122"/>
     </row>
@@ -2475,10 +2475,10 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.000875563541077049</v>
+        <v>0.000876209429825342</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0000203465653558076</v>
+        <v>0.0000204429188032432</v>
       </c>
     </row>
     <row r="124">
@@ -2489,7 +2489,7 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.000633484982856941</v>
+        <v>0.000633195594441095</v>
       </c>
       <c r="D124"/>
     </row>
@@ -2501,7 +2501,7 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.000523245441833582</v>
+        <v>0.000523529344719584</v>
       </c>
       <c r="D125"/>
     </row>
@@ -2513,7 +2513,7 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D126"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>15.942447140969</v>
+        <v>16.1455736191922</v>
       </c>
       <c r="D2" t="n">
-        <v>0.300440816764684</v>
+        <v>0.305552468217153</v>
       </c>
     </row>
     <row r="3">
@@ -2564,10 +2564,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>11.1787729386202</v>
+        <v>11.3906787774023</v>
       </c>
       <c r="D3" t="n">
-        <v>2.94460434793981</v>
+        <v>3.00054024635649</v>
       </c>
     </row>
     <row r="4">
@@ -2578,10 +2578,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>9.40053019487132</v>
+        <v>9.08294292291887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.630555766980555</v>
+        <v>0.602325234484184</v>
       </c>
     </row>
     <row r="5">
@@ -2592,10 +2592,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>8.28770331205634</v>
+        <v>8.40161069868793</v>
       </c>
       <c r="D5" t="n">
-        <v>0.668281225283254</v>
+        <v>0.677190845957553</v>
       </c>
     </row>
     <row r="6">
@@ -2606,10 +2606,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>7.72873300419545</v>
+        <v>7.80812922064845</v>
       </c>
       <c r="D6" t="n">
-        <v>0.163261976370674</v>
+        <v>0.16455427773711</v>
       </c>
     </row>
     <row r="7">
@@ -2620,10 +2620,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>7.61936437267391</v>
+        <v>7.70580868646754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.223889974744836</v>
+        <v>0.226594532904438</v>
       </c>
     </row>
     <row r="8">
@@ -2634,10 +2634,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>5.81056599552217</v>
+        <v>5.89190666916983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.099813522663096</v>
+        <v>0.101215686117624</v>
       </c>
     </row>
     <row r="9">
@@ -2648,10 +2648,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>4.59508593858663</v>
+        <v>4.6562194681692</v>
       </c>
       <c r="D9" t="n">
-        <v>0.100439062617691</v>
+        <v>0.101758636896761</v>
       </c>
     </row>
     <row r="10">
@@ -2659,13 +2659,13 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>3.72088503773932</v>
+        <v>3.193250233692</v>
       </c>
       <c r="D10" t="n">
-        <v>0.342009322956355</v>
+        <v>0.0655202488941631</v>
       </c>
     </row>
     <row r="11">
@@ -2673,13 +2673,13 @@
         <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>3.15034892229709</v>
+        <v>2.94336260979499</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0646529388543776</v>
+        <v>0.337420644595418</v>
       </c>
     </row>
     <row r="12">
@@ -2690,10 +2690,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>2.52519197337837</v>
+        <v>2.56269720780837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.355756963063507</v>
+        <v>0.361177924863553</v>
       </c>
     </row>
     <row r="13">
@@ -2704,10 +2704,10 @@
         <v>81</v>
       </c>
       <c r="C13" t="n">
-        <v>1.66853177770692</v>
+        <v>1.67483895765469</v>
       </c>
       <c r="D13" t="n">
-        <v>0.200058616123987</v>
+        <v>0.201529948094469</v>
       </c>
     </row>
     <row r="14">
@@ -2718,10 +2718,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>1.508592975179</v>
+        <v>1.51460726307645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0393988585022581</v>
+        <v>0.0397095256164362</v>
       </c>
     </row>
     <row r="15">
@@ -2732,10 +2732,10 @@
         <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1766861647843</v>
+        <v>1.19342317619039</v>
       </c>
       <c r="D15" t="n">
-        <v>0.120847864310866</v>
+        <v>0.122567720364319</v>
       </c>
     </row>
     <row r="16">
@@ -2746,10 +2746,10 @@
         <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>1.01529001985281</v>
+        <v>0.998618942625795</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0399822018599992</v>
+        <v>0.0385176414798821</v>
       </c>
     </row>
     <row r="17">
@@ -2760,10 +2760,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>0.981502204279665</v>
+        <v>0.993117234534015</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0261171014433507</v>
+        <v>0.0264409236612438</v>
       </c>
     </row>
     <row r="18">
@@ -2774,10 +2774,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>0.788172121277482</v>
+        <v>0.798781200573575</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0295282071946689</v>
+        <v>0.0299539993786084</v>
       </c>
     </row>
     <row r="19">
@@ -2788,10 +2788,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>0.718768824853531</v>
+        <v>0.728314693496191</v>
       </c>
       <c r="D19" t="n">
-        <v>0.087433555920052</v>
+        <v>0.0885673448298542</v>
       </c>
     </row>
     <row r="20">
@@ -2802,10 +2802,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.695440746917527</v>
+        <v>0.705470331144227</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0316640313558494</v>
+        <v>0.0321033178827312</v>
       </c>
     </row>
     <row r="21">
@@ -2816,10 +2816,10 @@
         <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>0.655156109680629</v>
+        <v>0.664398163650344</v>
       </c>
       <c r="D21" t="n">
-        <v>0.101133634761853</v>
+        <v>0.10257599733231</v>
       </c>
     </row>
     <row r="22">
@@ -2830,10 +2830,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.647081369379292</v>
+        <v>0.655975242905002</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0789661974186818</v>
+        <v>0.0800591919133054</v>
       </c>
     </row>
     <row r="23">
@@ -2844,10 +2844,10 @@
         <v>96</v>
       </c>
       <c r="C23" t="n">
-        <v>0.643536273404259</v>
+        <v>0.652343431286092</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0555737293239417</v>
+        <v>0.0563520561215487</v>
       </c>
     </row>
     <row r="24">
@@ -2858,10 +2858,10 @@
         <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>0.618749277466473</v>
+        <v>0.6250514338696</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0720040262147317</v>
+        <v>0.0728959377836819</v>
       </c>
     </row>
     <row r="25">
@@ -2872,10 +2872,10 @@
         <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5738514319036</v>
+        <v>0.581370041694404</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0565435833350612</v>
+        <v>0.0572879664194589</v>
       </c>
     </row>
     <row r="26">
@@ -2886,10 +2886,10 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>0.55787953554294</v>
+        <v>0.565248583401867</v>
       </c>
       <c r="D26" t="n">
-        <v>0.220142187115431</v>
+        <v>0.223054136267222</v>
       </c>
     </row>
     <row r="27">
@@ -2900,10 +2900,10 @@
         <v>28</v>
       </c>
       <c r="C27" t="n">
-        <v>0.519929018143244</v>
+        <v>0.526844521027926</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0423728046158284</v>
+        <v>0.0429336149791881</v>
       </c>
     </row>
     <row r="28">
@@ -2914,10 +2914,10 @@
         <v>22</v>
       </c>
       <c r="C28" t="n">
-        <v>0.47770341579368</v>
+        <v>0.484635342954498</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0768589214136416</v>
+        <v>0.0780168403652889</v>
       </c>
     </row>
     <row r="29">
@@ -2928,10 +2928,10 @@
         <v>18</v>
       </c>
       <c r="C29" t="n">
-        <v>0.447771690635206</v>
+        <v>0.454406259252149</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00926220509053072</v>
+        <v>0.00941261687597047</v>
       </c>
     </row>
     <row r="30">
@@ -2942,10 +2942,10 @@
         <v>50</v>
       </c>
       <c r="C30" t="n">
-        <v>0.401368976897267</v>
+        <v>0.406784578837727</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0284640790427565</v>
+        <v>0.0288408938510205</v>
       </c>
     </row>
     <row r="31">
@@ -2956,10 +2956,10 @@
         <v>123</v>
       </c>
       <c r="C31" t="n">
-        <v>0.386078483792058</v>
+        <v>0.391370556391853</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0541771166713075</v>
+        <v>0.0549212435517679</v>
       </c>
     </row>
     <row r="32">
@@ -2970,10 +2970,10 @@
         <v>49</v>
       </c>
       <c r="C32" t="n">
-        <v>0.301462729345209</v>
+        <v>0.30566826425354</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0186280050766262</v>
+        <v>0.0188853610736706</v>
       </c>
     </row>
     <row r="33">
@@ -2984,10 +2984,10 @@
         <v>41</v>
       </c>
       <c r="C33" t="n">
-        <v>0.274540482711706</v>
+        <v>0.278446348778541</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0159679648328081</v>
+        <v>0.0161832301591396</v>
       </c>
     </row>
     <row r="34">
@@ -2998,10 +2998,10 @@
         <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>0.251029148380127</v>
+        <v>0.254295966643203</v>
       </c>
       <c r="D34" t="n">
-        <v>0.118066558167185</v>
+        <v>0.119599662170047</v>
       </c>
     </row>
     <row r="35">
@@ -3012,10 +3012,10 @@
         <v>60</v>
       </c>
       <c r="C35" t="n">
-        <v>0.24980593987073</v>
+        <v>0.253337831876229</v>
       </c>
       <c r="D35" t="n">
-        <v>0.137157739177543</v>
+        <v>0.139043368674031</v>
       </c>
     </row>
     <row r="36">
@@ -3026,10 +3026,10 @@
         <v>91</v>
       </c>
       <c r="C36" t="n">
-        <v>0.247390146751712</v>
+        <v>0.239940108965265</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0496296454434227</v>
+        <v>0.047033026978111</v>
       </c>
     </row>
     <row r="37">
@@ -3040,10 +3040,10 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.236672669894473</v>
+        <v>0.236550493571486</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0136685818442839</v>
+        <v>0.0135590742183688</v>
       </c>
     </row>
     <row r="38">
@@ -3054,10 +3054,10 @@
         <v>109</v>
       </c>
       <c r="C38" t="n">
-        <v>0.223413753122689</v>
+        <v>0.227459487336691</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0882127420494344</v>
+        <v>0.0898771701022783</v>
       </c>
     </row>
     <row r="39">
@@ -3068,10 +3068,10 @@
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>0.201740253839049</v>
+        <v>0.200479419853574</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0127362299980534</v>
+        <v>0.0123753696026022</v>
       </c>
     </row>
     <row r="40">
@@ -3082,10 +3082,10 @@
         <v>66</v>
       </c>
       <c r="C40" t="n">
-        <v>0.15645068591365</v>
+        <v>0.152784871631663</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0477361676717595</v>
+        <v>0.0464613691694384</v>
       </c>
     </row>
     <row r="41">
@@ -3096,10 +3096,10 @@
         <v>119</v>
       </c>
       <c r="C41" t="n">
-        <v>0.142220369873847</v>
+        <v>0.144215083513282</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0404313762934247</v>
+        <v>0.0409931333226437</v>
       </c>
     </row>
     <row r="42">
@@ -3110,10 +3110,10 @@
         <v>43</v>
       </c>
       <c r="C42" t="n">
-        <v>0.138638720020316</v>
+        <v>0.1406423844885</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03702259070827</v>
+        <v>0.0375469334006258</v>
       </c>
     </row>
     <row r="43">
@@ -3124,10 +3124,10 @@
         <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>0.130250407027724</v>
+        <v>0.131996507405069</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0202301973681645</v>
+        <v>0.0204959555924036</v>
       </c>
     </row>
     <row r="44">
@@ -3138,10 +3138,10 @@
         <v>51</v>
       </c>
       <c r="C44" t="n">
-        <v>0.127545334077143</v>
+        <v>0.129277821405616</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0156581949147364</v>
+        <v>0.0158644449057194</v>
       </c>
     </row>
     <row r="45">
@@ -3152,10 +3152,10 @@
         <v>42</v>
       </c>
       <c r="C45" t="n">
-        <v>0.127142066876816</v>
+        <v>0.128980575307602</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00802171919862632</v>
+        <v>0.00813957118733485</v>
       </c>
     </row>
     <row r="46">
@@ -3166,10 +3166,10 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.114685645244818</v>
+        <v>0.116360950573543</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0245655527752233</v>
+        <v>0.0249510391309751</v>
       </c>
     </row>
     <row r="47">
@@ -3180,10 +3180,10 @@
         <v>57</v>
       </c>
       <c r="C47" t="n">
-        <v>0.114047040966229</v>
+        <v>0.114576603402338</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0234521182427278</v>
+        <v>0.0237774292113185</v>
       </c>
     </row>
     <row r="48">
@@ -3194,10 +3194,10 @@
         <v>107</v>
       </c>
       <c r="C48" t="n">
-        <v>0.104390428708162</v>
+        <v>0.105749557970777</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0508227110452255</v>
+        <v>0.0514825495843906</v>
       </c>
     </row>
     <row r="49">
@@ -3208,10 +3208,10 @@
         <v>97</v>
       </c>
       <c r="C49" t="n">
-        <v>0.102923804598766</v>
+        <v>0.104478448570681</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0576833500162469</v>
+        <v>0.0585564615459557</v>
       </c>
     </row>
     <row r="50">
@@ -3222,10 +3222,10 @@
         <v>37</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0976664344296023</v>
+        <v>0.0986092963616454</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00231007176757483</v>
+        <v>0.00231903468806524</v>
       </c>
     </row>
     <row r="51">
@@ -3236,10 +3236,10 @@
         <v>55</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0953619931332502</v>
+        <v>0.0966898056701383</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00780962174929297</v>
+        <v>0.00791636611171422</v>
       </c>
     </row>
     <row r="52">
@@ -3250,10 +3250,10 @@
         <v>21</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0941089914940425</v>
+        <v>0.0954825390324774</v>
       </c>
       <c r="D52" t="n">
-        <v>0.010175590735565</v>
+        <v>0.0103303942610915</v>
       </c>
     </row>
     <row r="53">
@@ -3264,10 +3264,10 @@
         <v>26</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0916109235011632</v>
+        <v>0.0928533199587465</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0101276294945725</v>
+        <v>0.0102599425461149</v>
       </c>
     </row>
     <row r="54">
@@ -3275,13 +3275,13 @@
         <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0916016417953377</v>
+        <v>0.0904082582352053</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00845852166798351</v>
+        <v>0.00432275740982072</v>
       </c>
     </row>
     <row r="55">
@@ -3289,13 +3289,13 @@
         <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0907558606756054</v>
+        <v>0.0900956608547697</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00447485023430806</v>
+        <v>0.00800482913878275</v>
       </c>
     </row>
     <row r="56">
@@ -3306,10 +3306,10 @@
         <v>63</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0885522290175251</v>
+        <v>0.089791624208388</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00638457334892884</v>
+        <v>0.00647576319463214</v>
       </c>
     </row>
     <row r="57">
@@ -3320,10 +3320,10 @@
         <v>68</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0865829890787799</v>
+        <v>0.0880223381252298</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00842452844062233</v>
+        <v>0.00858133849174108</v>
       </c>
     </row>
     <row r="58">
@@ -3334,7 +3334,7 @@
         <v>131</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0794332681635743</v>
+        <v>0.080520581383524</v>
       </c>
       <c r="D58"/>
     </row>
@@ -3346,10 +3346,10 @@
         <v>52</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0790345272271987</v>
+        <v>0.079993965651741</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00679332165337884</v>
+        <v>0.00689552249204132</v>
       </c>
     </row>
     <row r="60">
@@ -3360,10 +3360,10 @@
         <v>132</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0687573298046294</v>
+        <v>0.0701732656617423</v>
       </c>
       <c r="D60" t="n">
-        <v>0.03564596445624</v>
+        <v>0.0364047096601004</v>
       </c>
     </row>
     <row r="61">
@@ -3374,10 +3374,10 @@
         <v>86</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0679534882445532</v>
+        <v>0.0689928129843044</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00688564056057069</v>
+        <v>0.00698901142106945</v>
       </c>
     </row>
     <row r="62">
@@ -3388,10 +3388,10 @@
         <v>82</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0621992603413215</v>
+        <v>0.0630863707981193</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00909501397317871</v>
+        <v>0.00921785215264765</v>
       </c>
     </row>
     <row r="63">
@@ -3402,10 +3402,10 @@
         <v>27</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0604233606267015</v>
+        <v>0.0612506592225904</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0195724390892119</v>
+        <v>0.0198458036605469</v>
       </c>
     </row>
     <row r="64">
@@ -3416,10 +3416,10 @@
         <v>39</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0579201647778259</v>
+        <v>0.0586290722609143</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00794071272003151</v>
+        <v>0.0080559223031116</v>
       </c>
     </row>
     <row r="65">
@@ -3427,13 +3427,13 @@
         <v>130</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0563901443258622</v>
+        <v>0.0564972173259957</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0102407849022143</v>
+        <v>0.0287704174234449</v>
       </c>
     </row>
     <row r="66">
@@ -3441,13 +3441,13 @@
         <v>130</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0557487039704928</v>
+        <v>0.0559530158151055</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0283878398361279</v>
+        <v>0.0181254687030527</v>
       </c>
     </row>
     <row r="67">
@@ -3455,13 +3455,13 @@
         <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0551314705330944</v>
+        <v>0.0559304096733157</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0178571239040387</v>
+        <v>0.00825682410273574</v>
       </c>
     </row>
     <row r="68">
@@ -3469,13 +3469,13 @@
         <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0551313845913738</v>
+        <v>0.0547964171152686</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00814205723575119</v>
+        <v>0.00965221378338962</v>
       </c>
     </row>
     <row r="69">
@@ -3486,10 +3486,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="n">
-        <v>0.054303937705371</v>
+        <v>0.0533686607917045</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00672248951769872</v>
+        <v>0.00643239255487694</v>
       </c>
     </row>
     <row r="70">
@@ -3500,10 +3500,10 @@
         <v>38</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0473639718829265</v>
+        <v>0.0480434779380598</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00277216827582102</v>
+        <v>0.00281141695943564</v>
       </c>
     </row>
     <row r="71">
@@ -3514,7 +3514,7 @@
         <v>134</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0458693021253724</v>
+        <v>0.0465844386609021</v>
       </c>
       <c r="D71"/>
     </row>
@@ -3526,7 +3526,7 @@
         <v>135</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0420873794155875</v>
+        <v>0.0427288871790919</v>
       </c>
       <c r="D72"/>
     </row>
@@ -3538,10 +3538,10 @@
         <v>78</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0418099595414685</v>
+        <v>0.0423765041498838</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0236734293086432</v>
+        <v>0.0239798555752528</v>
       </c>
     </row>
     <row r="74">
@@ -3552,10 +3552,10 @@
         <v>104</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0404427986500547</v>
+        <v>0.0405278789246804</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00446678998923083</v>
+        <v>0.00449101997007153</v>
       </c>
     </row>
     <row r="75">
@@ -3566,10 +3566,10 @@
         <v>83</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0397822219382303</v>
+        <v>0.040320883277201</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00534862034970084</v>
+        <v>0.00542102753250326</v>
       </c>
     </row>
     <row r="76">
@@ -3580,10 +3580,10 @@
         <v>59</v>
       </c>
       <c r="C76" t="n">
-        <v>0.037239979900959</v>
+        <v>0.0377640386805224</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0046423246437133</v>
+        <v>0.00470575262805252</v>
       </c>
     </row>
     <row r="77">
@@ -3594,10 +3594,10 @@
         <v>48</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0348180849197775</v>
+        <v>0.0352781756278973</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00725469252960738</v>
+        <v>0.00734905707440079</v>
       </c>
     </row>
     <row r="78">
@@ -3608,10 +3608,10 @@
         <v>76</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0318192631681622</v>
+        <v>0.0322710944588589</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00546686492924663</v>
+        <v>0.00554832337401497</v>
       </c>
     </row>
     <row r="79">
@@ -3622,10 +3622,10 @@
         <v>92</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0317102317719523</v>
+        <v>0.0321347901610584</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00706751840573821</v>
+        <v>0.00715979378572593</v>
       </c>
     </row>
     <row r="80">
@@ -3636,10 +3636,10 @@
         <v>61</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0286455786623522</v>
+        <v>0.029043204390105</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00344630300614833</v>
+        <v>0.00349213504192394</v>
       </c>
     </row>
     <row r="81">
@@ -3650,10 +3650,10 @@
         <v>44</v>
       </c>
       <c r="C81" t="n">
-        <v>0.026197242278464</v>
+        <v>0.0265918454486327</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00343924879521813</v>
+        <v>0.0034928416871226</v>
       </c>
     </row>
     <row r="82">
@@ -3664,10 +3664,10 @@
         <v>32</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0258934382961188</v>
+        <v>0.0262491258921024</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00900491434123902</v>
+        <v>0.00912560058852466</v>
       </c>
     </row>
     <row r="83">
@@ -3678,10 +3678,10 @@
         <v>30</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0247384102184029</v>
+        <v>0.0250860268382721</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00115861941766982</v>
+        <v>0.0011748484305198</v>
       </c>
     </row>
     <row r="84">
@@ -3692,10 +3692,10 @@
         <v>136</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0240739661291511</v>
+        <v>0.0244147201912597</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00722331409795449</v>
+        <v>0.00733015845317589</v>
       </c>
     </row>
     <row r="85">
@@ -3706,10 +3706,10 @@
         <v>65</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0229731099826578</v>
+        <v>0.022460435194225</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0030838024670879</v>
+        <v>0.00291706082641546</v>
       </c>
     </row>
     <row r="86">
@@ -3720,10 +3720,10 @@
         <v>75</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0190883150333064</v>
+        <v>0.019373927824829</v>
       </c>
       <c r="D86" t="n">
-        <v>0.012838001249836</v>
+        <v>0.0130313917988485</v>
       </c>
     </row>
     <row r="87">
@@ -3734,10 +3734,10 @@
         <v>74</v>
       </c>
       <c r="C87" t="n">
-        <v>0.017400018579225</v>
+        <v>0.0176650311910475</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0039132560543665</v>
+        <v>0.00397646207922707</v>
       </c>
     </row>
     <row r="88">
@@ -3748,10 +3748,10 @@
         <v>137</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0171348024294323</v>
+        <v>0.017485633028603</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00801067764061384</v>
+        <v>0.00820541246828763</v>
       </c>
     </row>
     <row r="89">
@@ -3762,10 +3762,10 @@
         <v>72</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0170419853711769</v>
+        <v>0.0172826710829321</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00815725481652204</v>
+        <v>0.00826073395968249</v>
       </c>
     </row>
     <row r="90">
@@ -3776,10 +3776,10 @@
         <v>87</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0168188806644815</v>
+        <v>0.0170667374487117</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00457282023635471</v>
+        <v>0.00464193813517276</v>
       </c>
     </row>
     <row r="91">
@@ -3790,10 +3790,10 @@
         <v>73</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0150511740605594</v>
+        <v>0.0152714499495797</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00780353305785579</v>
+        <v>0.0079175190987513</v>
       </c>
     </row>
     <row r="92">
@@ -3804,10 +3804,10 @@
         <v>70</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0141565493962822</v>
+        <v>0.0143620097986818</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00493869471385782</v>
+        <v>0.00500606145536849</v>
       </c>
     </row>
     <row r="93">
@@ -3818,10 +3818,10 @@
         <v>58</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0140572294145009</v>
+        <v>0.0142599484370969</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00206737573346722</v>
+        <v>0.00209716350582463</v>
       </c>
     </row>
     <row r="94">
@@ -3832,10 +3832,10 @@
         <v>101</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0132393793539659</v>
+        <v>0.0134358834712381</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00029825902958435</v>
+        <v>0.000289288718725805</v>
       </c>
     </row>
     <row r="95">
@@ -3846,10 +3846,10 @@
         <v>62</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0123475621192286</v>
+        <v>0.0125175053335992</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00139722014161033</v>
+        <v>0.00141592241424564</v>
       </c>
     </row>
     <row r="96">
@@ -3860,10 +3860,10 @@
         <v>94</v>
       </c>
       <c r="C96" t="n">
-        <v>0.00911741390297989</v>
+        <v>0.00924559277820211</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00334214614523539</v>
+        <v>0.00338989481791672</v>
       </c>
     </row>
     <row r="97">
@@ -3874,7 +3874,7 @@
         <v>106</v>
       </c>
       <c r="C97" t="n">
-        <v>0.00872666554662074</v>
+        <v>0.0088544107610955</v>
       </c>
       <c r="D97"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>67</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00832844026056879</v>
+        <v>0.00844770334494201</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00387134051863828</v>
+        <v>0.00392651183649352</v>
       </c>
     </row>
     <row r="99">
@@ -3900,7 +3900,7 @@
         <v>138</v>
       </c>
       <c r="C99" t="n">
-        <v>0.00699284862785791</v>
+        <v>0.00708793956337197</v>
       </c>
       <c r="D99"/>
     </row>
@@ -3912,7 +3912,7 @@
         <v>139</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00685213338398429</v>
+        <v>0.00695981874693831</v>
       </c>
       <c r="D100"/>
     </row>
@@ -3924,10 +3924,10 @@
         <v>79</v>
       </c>
       <c r="C101" t="n">
-        <v>0.00674699801244191</v>
+        <v>0.00684574333824053</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00205567342838677</v>
+        <v>0.00208612220260079</v>
       </c>
     </row>
     <row r="102">
@@ -3938,10 +3938,10 @@
         <v>90</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00657396868162012</v>
+        <v>0.00667159769397817</v>
       </c>
       <c r="D102" t="n">
-        <v>0.000190007450251373</v>
+        <v>0.000194466533363914</v>
       </c>
     </row>
     <row r="103">
@@ -3952,7 +3952,7 @@
         <v>99</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00635381464066557</v>
+        <v>0.00645145624132455</v>
       </c>
       <c r="D103"/>
     </row>
@@ -3964,7 +3964,7 @@
         <v>140</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00547213852895987</v>
+        <v>0.00554877761935734</v>
       </c>
       <c r="D104"/>
     </row>
@@ -3976,10 +3976,10 @@
         <v>141</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00492778367063607</v>
+        <v>0.00499758242403665</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00126108160336021</v>
+        <v>0.00127838625142545</v>
       </c>
     </row>
     <row r="106">
@@ -3990,7 +3990,7 @@
         <v>142</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00479245410792048</v>
+        <v>0.00485579345255424</v>
       </c>
       <c r="D106"/>
     </row>
@@ -4002,10 +4002,10 @@
         <v>120</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00446103418602026</v>
+        <v>0.00451916797789277</v>
       </c>
       <c r="D107" t="n">
-        <v>0.00290466293325108</v>
+        <v>0.00294227844459761</v>
       </c>
     </row>
     <row r="108">
@@ -4016,7 +4016,7 @@
         <v>121</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00436145637907712</v>
+        <v>0.00442560931148686</v>
       </c>
       <c r="D108"/>
     </row>
@@ -4028,7 +4028,7 @@
         <v>143</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00325255035808691</v>
+        <v>0.00329602770793533</v>
       </c>
       <c r="D109"/>
     </row>
@@ -4040,7 +4040,7 @@
         <v>102</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00307324728166082</v>
+        <v>0.0031156719040542</v>
       </c>
       <c r="D110"/>
     </row>
@@ -4052,10 +4052,10 @@
         <v>64</v>
       </c>
       <c r="C111" t="n">
-        <v>0.00307264568961657</v>
+        <v>0.00311393073780596</v>
       </c>
       <c r="D111" t="n">
-        <v>0.000565691955411315</v>
+        <v>0.000573125122682993</v>
       </c>
     </row>
     <row r="112">
@@ -4066,10 +4066,10 @@
         <v>100</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00289852776366709</v>
+        <v>0.00294004626848082</v>
       </c>
       <c r="D112" t="n">
-        <v>0.00136424539014174</v>
+        <v>0.00138350924121507</v>
       </c>
     </row>
     <row r="113">
@@ -4080,10 +4080,10 @@
         <v>47</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00255478952847988</v>
+        <v>0.00259126164951908</v>
       </c>
       <c r="D113" t="n">
-        <v>0.000170339576080511</v>
+        <v>0.000172263776544074</v>
       </c>
     </row>
     <row r="114">
@@ -4094,10 +4094,10 @@
         <v>144</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00255458899779847</v>
+        <v>0.0025902459692076</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0015350900421055</v>
+        <v>0.00155677877880343</v>
       </c>
     </row>
     <row r="115">
@@ -4108,10 +4108,10 @@
         <v>125</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00204151692577556</v>
+        <v>0.00206870863898209</v>
       </c>
       <c r="D115" t="n">
-        <v>0.000564269459936274</v>
+        <v>0.00057207264784769</v>
       </c>
     </row>
     <row r="116">
@@ -4122,10 +4122,10 @@
         <v>103</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00203217792546962</v>
+        <v>0.00206574865636007</v>
       </c>
       <c r="D116" t="n">
-        <v>0.000714249754356442</v>
+        <v>0.000725807296783265</v>
       </c>
     </row>
     <row r="117">
@@ -4136,10 +4136,10 @@
         <v>113</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00194119429058716</v>
+        <v>0.00196830138533306</v>
       </c>
       <c r="D117" t="n">
-        <v>0.000218279451539477</v>
+        <v>0.000221490591617043</v>
       </c>
     </row>
     <row r="118">
@@ -4150,10 +4150,10 @@
         <v>129</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00157554091664521</v>
+        <v>0.00159601102201996</v>
       </c>
       <c r="D118" t="n">
-        <v>0.000571561856747628</v>
+        <v>0.000578987834272048</v>
       </c>
     </row>
     <row r="119">
@@ -4164,7 +4164,7 @@
         <v>108</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00144055512081205</v>
+        <v>0.00146060632678113</v>
       </c>
       <c r="D119"/>
     </row>
@@ -4176,10 +4176,10 @@
         <v>115</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00140792591422165</v>
+        <v>0.00143173198649767</v>
       </c>
       <c r="D120" t="n">
-        <v>0.000759604411191498</v>
+        <v>0.000772387335902827</v>
       </c>
     </row>
     <row r="121">
@@ -4190,7 +4190,7 @@
         <v>105</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00131536668112807</v>
+        <v>0.00133472000703273</v>
       </c>
       <c r="D121"/>
     </row>
@@ -4202,7 +4202,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00119882970798518</v>
+        <v>0.00121501482746561</v>
       </c>
       <c r="D122"/>
     </row>
@@ -4214,10 +4214,10 @@
         <v>116</v>
       </c>
       <c r="C123" t="n">
-        <v>0.000950057074068544</v>
+        <v>0.000963996693343051</v>
       </c>
       <c r="D123" t="n">
-        <v>0.000155571131975538</v>
+        <v>0.000156710025883741</v>
       </c>
     </row>
     <row r="124">
@@ -4228,10 +4228,10 @@
         <v>146</v>
       </c>
       <c r="C124" t="n">
-        <v>0.000891215642693053</v>
+        <v>0.000904187632715698</v>
       </c>
       <c r="D124" t="n">
-        <v>0.000223268882374268</v>
+        <v>0.000227154640111694</v>
       </c>
     </row>
     <row r="125">
@@ -4242,7 +4242,7 @@
         <v>147</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00083423628193071</v>
+        <v>0.000848528351646672</v>
       </c>
       <c r="D125"/>
     </row>
@@ -4254,7 +4254,7 @@
         <v>85</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00082306385825182</v>
+        <v>0.000835034313222743</v>
       </c>
       <c r="D126"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>71</v>
       </c>
       <c r="C127" t="n">
-        <v>0.000809972069479376</v>
+        <v>0.000822613993985233</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0000171371325066804</v>
+        <v>0.0000183242180324971</v>
       </c>
     </row>
     <row r="128">
@@ -4280,7 +4280,7 @@
         <v>118</v>
       </c>
       <c r="C128" t="n">
-        <v>0.000730046269315004</v>
+        <v>0.000742375249378426</v>
       </c>
       <c r="D128"/>
     </row>
@@ -4292,10 +4292,10 @@
         <v>148</v>
       </c>
       <c r="C129" t="n">
-        <v>0.000724030348872524</v>
+        <v>0.000735004312260838</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000158042444228274</v>
+        <v>0.00015972644251395</v>
       </c>
     </row>
     <row r="130">
@@ -4306,7 +4306,7 @@
         <v>111</v>
       </c>
       <c r="C130" t="n">
-        <v>0.000716009121615885</v>
+        <v>0.000725602014520294</v>
       </c>
       <c r="D130"/>
     </row>
@@ -4318,7 +4318,7 @@
         <v>110</v>
       </c>
       <c r="C131" t="n">
-        <v>0.000631700293700563</v>
+        <v>0.000640604082168272</v>
       </c>
       <c r="D131"/>
     </row>
@@ -4330,7 +4330,7 @@
         <v>149</v>
       </c>
       <c r="C132" t="n">
-        <v>0.000566098113637333</v>
+        <v>0.000574875056296873</v>
       </c>
       <c r="D132"/>
     </row>
@@ -4342,10 +4342,10 @@
         <v>150</v>
       </c>
       <c r="C133" t="n">
-        <v>0.000464629588840843</v>
+        <v>0.000472204286525125</v>
       </c>
       <c r="D133" t="n">
-        <v>0.000143356367316521</v>
+        <v>0.000146101268075453</v>
       </c>
     </row>
     <row r="134">
@@ -4356,7 +4356,7 @@
         <v>151</v>
       </c>
       <c r="C134" t="n">
-        <v>0.000441539913237802</v>
+        <v>0.000447682861862285</v>
       </c>
       <c r="D134"/>
     </row>
@@ -4368,7 +4368,7 @@
         <v>152</v>
       </c>
       <c r="C135" t="n">
-        <v>0.000264929677390722</v>
+        <v>0.000268603913229877</v>
       </c>
       <c r="D135"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>153</v>
       </c>
       <c r="C136" t="n">
-        <v>0.000250262290407152</v>
+        <v>0.000254558505494002</v>
       </c>
       <c r="D136"/>
     </row>
@@ -4392,7 +4392,7 @@
         <v>117</v>
       </c>
       <c r="C137" t="n">
-        <v>0.000166841526938102</v>
+        <v>0.000169705670329334</v>
       </c>
       <c r="D137"/>
     </row>
@@ -4404,7 +4404,7 @@
         <v>95</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00013094653496464</v>
+        <v>0.000132792945866456</v>
       </c>
       <c r="D138"/>
     </row>
